--- a/dataproduct.api/wwwroot/templates/BM_TongHopSoTheoDoiSanXuat.xlsx
+++ b/dataproduct.api/wwwroot/templates/BM_TongHopSoTheoDoiSanXuat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software\03. ThongKePKH\DATAPRODUCT_V2\dataproduct.api\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4BCDD1-7B2C-4152-B8C4-02323EB7486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0DAFEF-8F93-4DD4-A546-49A7786A6BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>TỔNG HỢP DỮ LIỆU SỔ THEO DÕI SẢN XUẤT THEO NGÀY</t>
   </si>
   <si>
-    <t>Loại mác phôi</t>
-  </si>
-  <si>
     <t>Loại phôi</t>
   </si>
   <si>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t>Tình trạng</t>
+  </si>
+  <si>
+    <t>Xưởng cán</t>
   </si>
 </sst>
 </file>
@@ -628,43 +628,43 @@
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
